--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTaxGlobal.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importTaxGlobal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinhaochen\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3229C489-65C8-4352-B266-B6A4AA8B9E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F21C499-B455-4015-BEBB-0E5611E02F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,13 +46,7 @@
     <t>美元</t>
   </si>
   <si>
-    <t>当地币折美元汇率</t>
-  </si>
-  <si>
     <t>人民币</t>
-  </si>
-  <si>
-    <t>人民币折美元汇率</t>
   </si>
   <si>
     <t>现金流入</t>
@@ -160,6 +154,14 @@
   </si>
   <si>
     <t>占位符</t>
+  </si>
+  <si>
+    <t>当地币折美元</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民币折美元</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -273,7 +275,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -283,12 +285,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -297,18 +305,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,74 +588,74 @@
     <col min="2" max="2" width="31.36328125" customWidth="1"/>
     <col min="3" max="3" width="17.1796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="21.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="25" style="11" customWidth="1"/>
+    <col min="6" max="6" width="25" customWidth="1"/>
     <col min="9" max="9" width="20.81640625" customWidth="1"/>
     <col min="11" max="11" width="23.453125" customWidth="1"/>
     <col min="13" max="13" width="25.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="8"/>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="8"/>
+      <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7" t="s">
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="I2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="K2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>10</v>
+      <c r="M2" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -667,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -675,7 +671,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -683,7 +679,7 @@
         <v>1.2</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -691,7 +687,7 @@
         <v>1.3</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -699,7 +695,7 @@
         <v>1.4</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -707,7 +703,7 @@
         <v>1.5</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -715,7 +711,7 @@
         <v>1.6</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -723,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -731,7 +727,7 @@
         <v>2.1</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -739,7 +735,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -747,7 +743,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -755,7 +751,7 @@
         <v>2.4</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -763,23 +759,23 @@
         <v>2.5</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -787,7 +783,7 @@
         <v>2.6</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -795,7 +791,7 @@
         <v>2.7</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -803,7 +799,7 @@
         <v>2.8</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.2" x14ac:dyDescent="0.3">
@@ -811,38 +807,38 @@
         <v>2.9</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="J1:M1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:M1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
